--- a/doc/音效需求表.xlsx
+++ b/doc/音效需求表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{7595151B-608F-49DA-84AB-7AB7C1D6E6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BA9E862-8E84-4689-82A2-E38DD794F1A6}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{7595151B-608F-49DA-84AB-7AB7C1D6E6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{797B96DB-BD3E-45A8-BA47-E028C0C2586F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{6F0AFF27-7857-43E5-B821-C8629BDF6EC9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -166,10 +166,6 @@
   </si>
   <si>
     <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已有</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -702,7 +698,7 @@
         <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -737,19 +733,16 @@
       <c r="C14" t="s">
         <v>28</v>
       </c>
-      <c r="F14" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
         <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
